--- a/gamedata/Effect.xlsx
+++ b/gamedata/Effect.xlsx
@@ -9,7 +9,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="t84dSBWrkW3C/+lLDhIF9Xi2tUEWC2dZty9iK1lGcaE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="59IOp6KhDm3KXZvsqDvRn1+PuQA0GC6qcd/1ho7IHmQ="/>
     </ext>
   </extLst>
 </workbook>
@@ -78,7 +78,7 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhVoOb6IlTNKXe1PkyX7S4ojGDFNw=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mjwAogtg0D84JMjd1t/0bj+G6S9Gw=="/>
     </ext>
   </extLst>
 </comments>
@@ -111,13 +111,13 @@
     <t>Group</t>
   </si>
   <si>
-    <t>TargetType</t>
+    <t>TargetKind</t>
   </si>
   <si>
     <t>TargetCount</t>
   </si>
   <si>
-    <t>TriggerType</t>
+    <t>TriggerKind</t>
   </si>
   <si>
     <t>TriggerCond</t>
@@ -247,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -256,6 +256,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -636,13 +639,13 @@
       <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="1" t="s">

--- a/gamedata/Effect.xlsx
+++ b/gamedata/Effect.xlsx
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>1</v>
@@ -1133,22 +1133,52 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" s="4">
       <c r="A10" s="1" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
+      <c r="B10" s="3" t="n">
+        <v>421</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>雙人款待</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="n"/>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>self.sate += 2</t>
+        </is>
+      </c>
       <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
@@ -1161,22 +1191,52 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" s="4">
       <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
+      <c r="B11" s="3" t="n">
+        <v>422</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>回甘減費</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3" t="n"/>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>cardCostAdd(self, -1)</t>
+        </is>
+      </c>
       <c r="R11" s="3" t="n"/>
       <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="n"/>
@@ -1189,22 +1249,52 @@
     </row>
     <row r="12" ht="15.75" customHeight="1" s="4">
       <c r="A12" s="1" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
+      <c r="B12" s="3" t="n">
+        <v>423</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>補給抽牌</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
-      <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="3" t="n"/>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>deckToHand(deckTop[2], false)</t>
+        </is>
+      </c>
       <c r="R12" s="3" t="n"/>
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n"/>
@@ -1217,22 +1307,52 @@
     </row>
     <row r="13" ht="15.75" customHeight="1" s="4">
       <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
+      <c r="B13" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>棄牌回收</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3" t="n"/>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>dropToHand(dropPick[1, 0])</t>
+        </is>
+      </c>
       <c r="R13" s="3" t="n"/>
       <c r="S13" s="3" t="n"/>
       <c r="T13" s="3" t="n"/>
@@ -1245,22 +1365,52 @@
     </row>
     <row r="14" ht="15.75" customHeight="1" s="4">
       <c r="A14" s="1" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
+      <c r="B14" s="3" t="n">
+        <v>425</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>斷捨離</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n"/>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>handToDrop(handPick[2, 0])</t>
+        </is>
+      </c>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="n"/>
@@ -1273,22 +1423,52 @@
     </row>
     <row r="15" ht="15.75" customHeight="1" s="4">
       <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
+      <c r="B15" s="3" t="n">
+        <v>426</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>冷凍封存</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H15" s="3" t="n"/>
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
-      <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="3" t="n"/>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>handToExile(handPick[1, 0])</t>
+        </is>
+      </c>
       <c r="R15" s="3" t="n"/>
       <c r="S15" s="3" t="n"/>
       <c r="T15" s="3" t="n"/>
@@ -1301,22 +1481,52 @@
     </row>
     <row r="16" ht="15.75" customHeight="1" s="4">
       <c r="A16" s="1" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
+      <c r="B16" s="3" t="n">
+        <v>427</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>大量備餐</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
-      <c r="P16" s="3" t="n"/>
-      <c r="Q16" s="3" t="n"/>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>handRoll(none, 7, 2)</t>
+        </is>
+      </c>
       <c r="R16" s="3" t="n"/>
       <c r="S16" s="3" t="n"/>
       <c r="T16" s="3" t="n"/>
@@ -1329,22 +1539,52 @@
     </row>
     <row r="17" ht="15.75" customHeight="1" s="4">
       <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
+      <c r="B17" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>菜單變身</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H17" s="3" t="n"/>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
-      <c r="P17" s="3" t="n"/>
-      <c r="Q17" s="3" t="n"/>
+      <c r="K17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>handMorph(handPick[1, 0], 8)</t>
+        </is>
+      </c>
       <c r="R17" s="3" t="n"/>
       <c r="S17" s="3" t="n"/>
       <c r="T17" s="3" t="n"/>
@@ -1357,22 +1597,52 @@
     </row>
     <row r="18" ht="15.75" customHeight="1" s="4">
       <c r="A18" s="1" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
+      <c r="B18" s="3" t="n">
+        <v>429</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>客滿招攬</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H18" s="3" t="n"/>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
-      <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="3" t="n"/>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>waitAdd(none, 512, 2)</t>
+        </is>
+      </c>
       <c r="R18" s="3" t="n"/>
       <c r="S18" s="3" t="n"/>
       <c r="T18" s="3" t="n"/>
@@ -1385,22 +1655,52 @@
     </row>
     <row r="19" ht="15.75" customHeight="1" s="4">
       <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
+      <c r="B19" s="3" t="n">
+        <v>430</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>引導入座</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="3" t="n"/>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>guestSeat(none)</t>
+        </is>
+      </c>
       <c r="R19" s="3" t="n"/>
       <c r="S19" s="3" t="n"/>
       <c r="T19" s="3" t="n"/>
@@ -1413,22 +1713,52 @@
     </row>
     <row r="20" ht="15.75" customHeight="1" s="4">
       <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
+      <c r="B20" s="3" t="n">
+        <v>431</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>暫請離席</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H20" s="3" t="n"/>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
-      <c r="O20" s="3" t="n"/>
-      <c r="P20" s="3" t="n"/>
-      <c r="Q20" s="3" t="n"/>
+      <c r="K20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>guestRoam(self)</t>
+        </is>
+      </c>
       <c r="R20" s="3" t="n"/>
       <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n"/>
@@ -1441,23 +1771,61 @@
     </row>
     <row r="21" ht="15.75" customHeight="1" s="4">
       <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
+      <c r="B21" s="3" t="n">
+        <v>432</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>召回廣播</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>roundStart</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>roamSize &gt; 0</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
-      <c r="P21" s="3" t="n"/>
+      <c r="K21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q21" s="3" t="n"/>
-      <c r="R21" s="3" t="n"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>guestReturn(self)</t>
+        </is>
+      </c>
       <c r="S21" s="3" t="n"/>
       <c r="T21" s="3" t="n"/>
       <c r="U21" s="3" t="n"/>
@@ -1469,22 +1837,52 @@
     </row>
     <row r="22" ht="15.75" customHeight="1" s="4">
       <c r="A22" s="1" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
+      <c r="B22" s="3" t="n">
+        <v>433</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>卡牌化收編</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H22" s="3" t="n"/>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
-      <c r="O22" s="3" t="n"/>
-      <c r="P22" s="3" t="n"/>
-      <c r="Q22" s="3" t="n"/>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>cardify(self, 126)</t>
+        </is>
+      </c>
       <c r="R22" s="3" t="n"/>
       <c r="S22" s="3" t="n"/>
       <c r="T22" s="3" t="n"/>
@@ -1497,22 +1895,52 @@
     </row>
     <row r="23" ht="15.75" customHeight="1" s="4">
       <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
+      <c r="B23" s="3" t="n">
+        <v>434</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>護盾補充</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
-      <c r="P23" s="3" t="n"/>
-      <c r="Q23" s="3" t="n"/>
+      <c r="K23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>moraleShield += 3</t>
+        </is>
+      </c>
       <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n"/>
@@ -1525,22 +1953,52 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" s="4">
       <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
+      <c r="B24" s="3" t="n">
+        <v>435</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>格擋架勢</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
-      <c r="P24" s="3" t="n"/>
-      <c r="Q24" s="3" t="n"/>
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>moraleBlock += 1</t>
+        </is>
+      </c>
       <c r="R24" s="3" t="n"/>
       <c r="S24" s="3" t="n"/>
       <c r="T24" s="3" t="n"/>
@@ -1553,25 +2011,59 @@
     </row>
     <row r="25" ht="15.75" customHeight="1" s="4">
       <c r="A25" s="1" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
+      <c r="B25" s="3" t="n">
+        <v>436</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>嚴防死守</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
-      <c r="P25" s="3" t="n"/>
+      <c r="K25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q25" s="3" t="n"/>
       <c r="R25" s="3" t="n"/>
-      <c r="S25" s="3" t="n"/>
-      <c r="T25" s="3" t="n"/>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>effectImmuneAdd(self, 4)</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t>effectImmuneDel(self, 4)</t>
+        </is>
+      </c>
       <c r="U25" s="3" t="n"/>
       <c r="V25" s="3" t="n"/>
       <c r="W25" s="3" t="n"/>
@@ -1581,22 +2073,52 @@
     </row>
     <row r="26" ht="15.75" customHeight="1" s="4">
       <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
+      <c r="B26" s="3" t="n">
+        <v>438</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>借力使力</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
-      <c r="P26" s="3" t="n"/>
-      <c r="Q26" s="3" t="n"/>
+      <c r="K26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>effectRun(guestRand[1], 411, 0)</t>
+        </is>
+      </c>
       <c r="R26" s="3" t="n"/>
       <c r="S26" s="3" t="n"/>
       <c r="T26" s="3" t="n"/>
@@ -1609,22 +2131,52 @@
     </row>
     <row r="27" ht="15.75" customHeight="1" s="4">
       <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
+      <c r="B27" s="3" t="n">
+        <v>439</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>氣氛清場</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
-      <c r="P27" s="3" t="n"/>
-      <c r="Q27" s="3" t="n"/>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>effectClear(none, 2)</t>
+        </is>
+      </c>
       <c r="R27" s="3" t="n"/>
       <c r="S27" s="3" t="n"/>
       <c r="T27" s="3" t="n"/>
@@ -1637,22 +2189,52 @@
     </row>
     <row r="28" ht="15.75" customHeight="1" s="4">
       <c r="A28" s="1" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
+      <c r="B28" s="3" t="n">
+        <v>441</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>牌庫洗牌</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
-      <c r="N28" s="3" t="n"/>
-      <c r="O28" s="3" t="n"/>
-      <c r="P28" s="3" t="n"/>
-      <c r="Q28" s="3" t="n"/>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>deckShuffle(none)</t>
+        </is>
+      </c>
       <c r="R28" s="3" t="n"/>
       <c r="S28" s="3" t="n"/>
       <c r="T28" s="3" t="n"/>
@@ -1665,22 +2247,52 @@
     </row>
     <row r="29" ht="15.75" customHeight="1" s="4">
       <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
+      <c r="B29" s="3" t="n">
+        <v>442</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>棄牌歸庫</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="n"/>
-      <c r="P29" s="3" t="n"/>
-      <c r="Q29" s="3" t="n"/>
+      <c r="K29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>dropToDeck(dropAll[0], true)</t>
+        </is>
+      </c>
       <c r="R29" s="3" t="n"/>
       <c r="S29" s="3" t="n"/>
       <c r="T29" s="3" t="n"/>
@@ -1693,22 +2305,52 @@
     </row>
     <row r="30" ht="15.75" customHeight="1" s="4">
       <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
+      <c r="B30" s="3" t="n">
+        <v>443</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>複製食譜</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="n"/>
-      <c r="O30" s="3" t="n"/>
-      <c r="P30" s="3" t="n"/>
-      <c r="Q30" s="3" t="n"/>
+      <c r="K30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>handCopy(handPick[1, 0], 1, 451)</t>
+        </is>
+      </c>
       <c r="R30" s="3" t="n"/>
       <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="n"/>
@@ -1721,22 +2363,52 @@
     </row>
     <row r="31" ht="15.75" customHeight="1" s="4">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
+      <c r="B31" s="3" t="n">
+        <v>444</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>附魔調味</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H31" s="3" t="n"/>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
-      <c r="P31" s="3" t="n"/>
-      <c r="Q31" s="3" t="n"/>
+      <c r="K31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>cardEffectAdd(handPick[1, 0], 451)</t>
+        </is>
+      </c>
       <c r="R31" s="3" t="n"/>
       <c r="S31" s="3" t="n"/>
       <c r="T31" s="3" t="n"/>
@@ -1749,23 +2421,57 @@
     </row>
     <row r="32" ht="15.75" customHeight="1" s="4">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
+      <c r="B32" s="3" t="n">
+        <v>445</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>客來鈴鐺</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>guestSeat</t>
+        </is>
+      </c>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
-      <c r="P32" s="3" t="n"/>
+      <c r="K32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q32" s="3" t="n"/>
-      <c r="R32" s="3" t="n"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>score += 1</t>
+        </is>
+      </c>
       <c r="S32" s="3" t="n"/>
       <c r="T32" s="3" t="n"/>
       <c r="U32" s="3" t="n"/>
@@ -1777,23 +2483,61 @@
     </row>
     <row r="33" ht="15.75" customHeight="1" s="4">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
+      <c r="B33" s="3" t="n">
+        <v>446</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>防災演練</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>damageValue &gt;= 1</t>
+        </is>
+      </c>
       <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
-      <c r="P33" s="3" t="n"/>
+      <c r="K33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" s="3" t="n"/>
-      <c r="R33" s="3" t="n"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>moraleShield += 2</t>
+        </is>
+      </c>
       <c r="S33" s="3" t="n"/>
       <c r="T33" s="3" t="n"/>
       <c r="U33" s="3" t="n"/>
@@ -1805,22 +2549,52 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" s="4">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
+      <c r="B34" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>加點服務</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="H34" s="3" t="n"/>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
-      <c r="O34" s="3" t="n"/>
-      <c r="P34" s="3" t="n"/>
-      <c r="Q34" s="3" t="n"/>
+      <c r="K34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>taskAdd(self, 0, 311)</t>
+        </is>
+      </c>
       <c r="R34" s="3" t="n"/>
       <c r="S34" s="3" t="n"/>
       <c r="T34" s="3" t="n"/>
@@ -1833,22 +2607,52 @@
     </row>
     <row r="35" ht="15.75" customHeight="1" s="4">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
+      <c r="B35" s="3" t="n">
+        <v>448</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>連鎖出餐</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H35" s="3" t="n"/>
       <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="n"/>
-      <c r="K35" s="3" t="n"/>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
-      <c r="O35" s="3" t="n"/>
-      <c r="P35" s="3" t="n"/>
-      <c r="Q35" s="3" t="n"/>
+      <c r="K35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>cardRun(handPick[1, 0], false, false)</t>
+        </is>
+      </c>
       <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="n"/>
       <c r="T35" s="3" t="n"/>
@@ -1861,22 +2665,52 @@
     </row>
     <row r="36" ht="15.75" customHeight="1" s="4">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="3" t="n"/>
+      <c r="B36" s="3" t="n">
+        <v>451</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>靈光調味</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n"/>
-      <c r="K36" s="3" t="n"/>
-      <c r="L36" s="3" t="n"/>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="n"/>
-      <c r="O36" s="3" t="n"/>
-      <c r="P36" s="3" t="n"/>
-      <c r="Q36" s="3" t="n"/>
+      <c r="K36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>energy += 1</t>
+        </is>
+      </c>
       <c r="R36" s="3" t="n"/>
       <c r="S36" s="3" t="n"/>
       <c r="T36" s="3" t="n"/>
@@ -1889,22 +2723,52 @@
     </row>
     <row r="37" ht="15.75" customHeight="1" s="4">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
+      <c r="B37" s="3" t="n">
+        <v>461</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>路過食客</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
-      <c r="K37" s="3" t="n"/>
-      <c r="L37" s="3" t="n"/>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
-      <c r="O37" s="3" t="n"/>
-      <c r="P37" s="3" t="n"/>
-      <c r="Q37" s="3" t="n"/>
+      <c r="K37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>guestSpawn(none, 514, 0)</t>
+        </is>
+      </c>
       <c r="R37" s="3" t="n"/>
       <c r="S37" s="3" t="n"/>
       <c r="T37" s="3" t="n"/>
@@ -1917,22 +2781,52 @@
     </row>
     <row r="38" ht="15.75" customHeight="1" s="4">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n"/>
+      <c r="B38" s="3" t="n">
+        <v>462</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>開店進貨</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H38" s="3" t="n"/>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
-      <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="n"/>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3" t="n"/>
-      <c r="O38" s="3" t="n"/>
-      <c r="P38" s="3" t="n"/>
-      <c r="Q38" s="3" t="n"/>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>deckRoll(none, 7, 6)</t>
+        </is>
+      </c>
       <c r="R38" s="3" t="n"/>
       <c r="S38" s="3" t="n"/>
       <c r="T38" s="3" t="n"/>
@@ -1945,22 +2839,52 @@
     </row>
     <row r="39" ht="15.75" customHeight="1" s="4">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="n"/>
+      <c r="B39" s="3" t="n">
+        <v>463</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>開店護盾</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n"/>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="n"/>
-      <c r="P39" s="3" t="n"/>
-      <c r="Q39" s="3" t="n"/>
+      <c r="K39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>moraleShield += 2</t>
+        </is>
+      </c>
       <c r="R39" s="3" t="n"/>
       <c r="S39" s="3" t="n"/>
       <c r="T39" s="3" t="n"/>
@@ -1973,22 +2897,52 @@
     </row>
     <row r="40" ht="15.75" customHeight="1" s="4">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
+      <c r="B40" s="3" t="n">
+        <v>464</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>招待回禮</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n"/>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
-      <c r="O40" s="3" t="n"/>
-      <c r="P40" s="3" t="n"/>
-      <c r="Q40" s="3" t="n"/>
+      <c r="K40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>score += 2</t>
+        </is>
+      </c>
       <c r="R40" s="3" t="n"/>
       <c r="S40" s="3" t="n"/>
       <c r="T40" s="3" t="n"/>
